--- a/data/trans_camb/IP18A01-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP18A01-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 14,4</t>
+          <t>-2,76; 14,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 11,86</t>
+          <t>-5,69; 12,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 12,51</t>
+          <t>-15,64; 15,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 14,04</t>
+          <t>-3,16; 13,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 10,96</t>
+          <t>-7,4; 10,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 7,08</t>
+          <t>-17,82; 7,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 12,26</t>
+          <t>-0,37; 12,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 8,74</t>
+          <t>-3,02; 8,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 5,85</t>
+          <t>-14,51; 5,09</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 99,87</t>
+          <t>-13,37; 90,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 85,04</t>
+          <t>-23,21; 80,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-72,09; 72,59</t>
+          <t>-70,95; 90,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 93,92</t>
+          <t>-14,43; 89,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 73,46</t>
+          <t>-30,24; 64,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,52; 43,18</t>
+          <t>-80,68; 48,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 72,64</t>
+          <t>-2,56; 73,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 56,13</t>
+          <t>-12,9; 55,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-66,5; 31,89</t>
+          <t>-66,09; 30,09</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 5,32</t>
+          <t>-3,61; 4,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 3,37</t>
+          <t>-4,55; 3,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 6,44</t>
+          <t>-8,28; 6,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 5,2</t>
+          <t>-3,12; 5,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 4,49</t>
+          <t>-3,95; 4,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 4,64</t>
+          <t>-8,17; 3,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 3,89</t>
+          <t>-1,75; 3,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 2,47</t>
+          <t>-2,84; 3,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 1,48</t>
+          <t>-7,27; 1,35</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-35,23; 109,53</t>
+          <t>-42,21; 97,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-50,95; 74,03</t>
+          <t>-51,88; 69,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 123,76</t>
+          <t>-100,0; 146,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 85,41</t>
+          <t>-32,75; 86,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,69; 76,96</t>
+          <t>-40,26; 71,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-86,3; 78,97</t>
+          <t>-100,0; 67,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 65,26</t>
+          <t>-20,57; 63,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,74; 39,01</t>
+          <t>-32,22; 50,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-87,2; 29,04</t>
+          <t>-86,16; 28,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 4,5</t>
+          <t>-5,26; 4,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 2,63</t>
+          <t>-5,82; 2,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 12,9</t>
+          <t>-4,76; 12,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 1,95</t>
+          <t>-5,61; 2,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 3,69</t>
+          <t>-5,02; 3,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,8; -2,36</t>
+          <t>-8,89; -2,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 2,31</t>
+          <t>-3,85; 2,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 2,17</t>
+          <t>-4,19; 2,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 2,9</t>
+          <t>-5,57; 2,61</t>
         </is>
       </c>
     </row>
@@ -1215,27 +1215,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-66,62; 170,69</t>
+          <t>-68,51; 156,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-70,23; 108,59</t>
+          <t>-70,87; 130,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 433,22</t>
+          <t>-84,59; 438,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-81,55; 114,46</t>
+          <t>-79,41; 127,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-69,28; 157,81</t>
+          <t>-67,29; 157,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-62,24; 81,85</t>
+          <t>-60,43; 64,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-56,49; 77,81</t>
+          <t>-58,94; 68,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-89,49; 111,87</t>
+          <t>-92,16; 89,01</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 0,35</t>
+          <t>-6,99; 0,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 7,04</t>
+          <t>-2,39; 7,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 15,41</t>
+          <t>-5,83; 15,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 4,08</t>
+          <t>-3,22; 4,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 3,76</t>
+          <t>-3,85; 3,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 7,4</t>
+          <t>-4,57; 7,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 1,3</t>
+          <t>-3,99; 1,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,59</t>
+          <t>-2,11; 4,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 5,58</t>
+          <t>-4,17; 7,38</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-84,86; 25,73</t>
+          <t>-85,53; 32,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,7; 185,4</t>
+          <t>-32,34; 197,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 364,12</t>
+          <t>-100,0; 381,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,17; 184,25</t>
+          <t>-58,5; 179,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-62,24; 152,54</t>
+          <t>-69,59; 165,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 356,65</t>
+          <t>-100,0; 390,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-64,6; 41,56</t>
+          <t>-60,78; 45,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,37; 129,27</t>
+          <t>-34,0; 117,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-76,29; 152,3</t>
+          <t>-76,78; 222,97</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 4,01</t>
+          <t>-1,38; 3,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,36</t>
+          <t>-1,61; 3,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 4,38</t>
+          <t>-5,31; 4,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 4,23</t>
+          <t>-1,1; 4,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 3,14</t>
+          <t>-2,17; 2,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -0,85</t>
+          <t>-7,22; -0,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 3,17</t>
+          <t>-0,5; 3,23</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,46</t>
+          <t>-1,21; 2,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,24; -0,16</t>
+          <t>-5,37; -0,09</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 56,93</t>
+          <t>-13,44; 54,28</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 47,06</t>
+          <t>-16,57; 49,71</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-60,37; 57,88</t>
+          <t>-58,42; 55,26</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 60,79</t>
+          <t>-11,48; 57,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-23,1; 44,36</t>
+          <t>-22,69; 38,09</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-76,14; -5,88</t>
+          <t>-76,76; -7,47</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 41,77</t>
+          <t>-5,42; 41,94</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 31,83</t>
+          <t>-13,4; 34,81</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-59,14; -1,87</t>
+          <t>-59,39; -0,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A01-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP18A01-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 14,1</t>
+          <t>-3,0; 15,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 12,33</t>
+          <t>-5,85; 12,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 15,34</t>
+          <t>-15,23; 13,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 13,85</t>
+          <t>-2,71; 15,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 10,18</t>
+          <t>-6,74; 10,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 7,82</t>
+          <t>-17,21; 7,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 12,26</t>
+          <t>-0,75; 11,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 8,97</t>
+          <t>-4,33; 8,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 5,09</t>
+          <t>-13,98; 5,22</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 90,27</t>
+          <t>-12,49; 102,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,21; 80,53</t>
+          <t>-23,2; 85,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-70,95; 90,91</t>
+          <t>-67,5; 86,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 89,04</t>
+          <t>-11,81; 100,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,24; 64,88</t>
+          <t>-28,84; 68,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,68; 48,36</t>
+          <t>-78,4; 50,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 73,35</t>
+          <t>-3,29; 69,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 55,56</t>
+          <t>-18,49; 52,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-66,09; 30,09</t>
+          <t>-64,44; 30,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 4,66</t>
+          <t>-3,55; 4,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 3,37</t>
+          <t>-4,92; 3,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 6,13</t>
+          <t>-8,29; 6,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 5,25</t>
+          <t>-2,97; 4,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 4,58</t>
+          <t>-3,66; 4,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 3,78</t>
+          <t>-7,82; 4,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,74</t>
+          <t>-1,65; 3,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 3,05</t>
+          <t>-2,9; 2,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 1,35</t>
+          <t>-6,84; 1,31</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,21; 97,12</t>
+          <t>-39,63; 89,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-51,88; 69,58</t>
+          <t>-53,74; 65,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 146,95</t>
+          <t>-100,0; 119,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,75; 86,15</t>
+          <t>-31,91; 79,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 71,68</t>
+          <t>-40,01; 79,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 67,98</t>
+          <t>-86,44; 77,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 63,07</t>
+          <t>-19,37; 62,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,22; 50,53</t>
+          <t>-33,14; 45,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-86,16; 28,97</t>
+          <t>-87,57; 22,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 4,24</t>
+          <t>-4,98; 4,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 2,89</t>
+          <t>-5,86; 2,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 12,64</t>
+          <t>-4,88; 13,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 2,29</t>
+          <t>-6,1; 1,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 3,41</t>
+          <t>-4,84; 3,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,89; -2,33</t>
+          <t>-9,5; -2,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 2,06</t>
+          <t>-4,38; 2,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 2,12</t>
+          <t>-3,94; 2,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 2,61</t>
+          <t>-5,55; 3,07</t>
         </is>
       </c>
     </row>
@@ -1215,27 +1215,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-68,51; 156,74</t>
+          <t>-63,21; 183,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-70,87; 130,35</t>
+          <t>-67,56; 114,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-84,59; 438,98</t>
+          <t>-100,0; 470,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-79,41; 127,76</t>
+          <t>-83,12; 101,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-67,29; 157,68</t>
+          <t>-64,66; 137,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-60,43; 64,61</t>
+          <t>-61,96; 62,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-58,94; 68,89</t>
+          <t>-55,43; 79,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-92,16; 89,01</t>
+          <t>-90,16; 100,76</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 0,82</t>
+          <t>-7,07; 0,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 7,07</t>
+          <t>-2,74; 7,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 15,82</t>
+          <t>-6,29; 15,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 4,13</t>
+          <t>-3,19; 4,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 3,91</t>
+          <t>-3,53; 3,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 7,66</t>
+          <t>-4,79; 7,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 1,34</t>
+          <t>-4,0; 1,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,34</t>
+          <t>-1,92; 4,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 7,38</t>
+          <t>-4,19; 6,84</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-85,53; 32,53</t>
+          <t>-84,71; 37,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,34; 197,18</t>
+          <t>-39,5; 187,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 381,99</t>
+          <t>-100,0; 394,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-58,5; 179,37</t>
+          <t>-57,0; 184,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-69,59; 165,83</t>
+          <t>-63,1; 154,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 390,67</t>
+          <t>-100,0; 329,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-60,78; 45,9</t>
+          <t>-61,37; 43,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,0; 117,13</t>
+          <t>-32,18; 116,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-76,78; 222,97</t>
+          <t>-75,08; 183,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 3,93</t>
+          <t>-1,71; 3,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,65</t>
+          <t>-1,83; 3,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 4,05</t>
+          <t>-5,33; 4,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 4,17</t>
+          <t>-0,77; 4,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 2,64</t>
+          <t>-2,19; 2,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -0,77</t>
+          <t>-7,16; -0,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,23</t>
+          <t>-0,44; 3,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,55</t>
+          <t>-1,1; 2,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,37; -0,09</t>
+          <t>-5,48; -0,09</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 54,28</t>
+          <t>-16,84; 49,02</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 49,71</t>
+          <t>-19,13; 50,21</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-58,42; 55,26</t>
+          <t>-58,45; 60,39</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 57,1</t>
+          <t>-8,2; 63,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-22,69; 38,09</t>
+          <t>-23,21; 41,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-76,76; -7,47</t>
+          <t>-78,11; -10,5</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 41,94</t>
+          <t>-4,39; 44,3</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 34,81</t>
+          <t>-12,52; 30,19</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-59,39; -0,63</t>
+          <t>-61,35; -1,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A01-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP18A01-Edad-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación</t>
+          <t>Menores cuya última consulta médica fue por vacunación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,94</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,06</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-7,9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5,63</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3,52</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,9</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,94</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,06</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-7,16</t>
+          <t>-4,29</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-5,16</t>
+          <t>-6,11</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 15,26</t>
+          <t>-3,57; 14,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 12,36</t>
+          <t>-6,91; 10,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,23; 13,26</t>
+          <t>-18,35; 5,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 15,05</t>
+          <t>-3,42; 14,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 10,21</t>
+          <t>-5,23; 11,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,21; 7,39</t>
+          <t>-16,27; 10,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 11,43</t>
+          <t>-0,09; 12,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 8,65</t>
+          <t>-3,69; 8,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 5,22</t>
+          <t>-15,4; 4,71</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30,24%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10,48%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-40,24%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>28,47%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>17,83%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-14,65%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>30,24%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-36,48%</t>
+          <t>-21,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-26,21%</t>
+          <t>-31,02%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 102,67</t>
+          <t>-14,76; 93,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 85,48</t>
+          <t>-27,86; 73,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,5; 86,28</t>
+          <t>-81,19; 37,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 100,32</t>
+          <t>-14,05; 99,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,84; 68,05</t>
+          <t>-21,71; 85,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-78,4; 50,0</t>
+          <t>-75,47; 63,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 69,76</t>
+          <t>-1,53; 72,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 52,8</t>
+          <t>-14,63; 56,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-64,44; 30,0</t>
+          <t>-69,1; 26,87</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,07</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,75</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,76</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,8</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,24</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,07</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,39</t>
+          <t>-4,05</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,73</t>
+          <t>-3,86</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 4,33</t>
+          <t>-2,88; 5,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 3,32</t>
+          <t>-3,62; 4,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 6,08</t>
+          <t>-8,38; 3,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 4,87</t>
+          <t>-3,0; 5,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 4,75</t>
+          <t>-4,5; 3,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 4,53</t>
+          <t>-8,37; 7,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,84</t>
+          <t>-1,78; 3,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 2,73</t>
+          <t>-2,96; 2,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 1,31</t>
+          <t>-7,09; 1,5</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13,49%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-47,18%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>10,97%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-11,48%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-61,04%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-42,59%</t>
+          <t>-58,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-50,08%</t>
+          <t>-51,82%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,63; 89,06</t>
+          <t>-30,37; 85,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-53,74; 65,11</t>
+          <t>-36,69; 76,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 119,93</t>
+          <t>-88,16; 65,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,91; 79,81</t>
+          <t>-35,23; 109,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,01; 79,61</t>
+          <t>-50,95; 74,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-86,44; 77,66</t>
+          <t>-100,0; 140,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 62,18</t>
+          <t>-20,57; 65,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,14; 45,68</t>
+          <t>-33,74; 39,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-87,57; 22,83</t>
+          <t>-88,01; 31,64</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,68</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,4</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-4,75</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-0,07</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,18</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,93</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,68</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,75</t>
+          <t>1,41</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,16</t>
+          <t>-1,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 4,69</t>
+          <t>-6,18; 1,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 2,72</t>
+          <t>-5,07; 3,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 13,18</t>
+          <t>-8,8; -2,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 1,96</t>
+          <t>-4,9; 4,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 3,3</t>
+          <t>-6,07; 2,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,5; -2,37</t>
+          <t>-5,17; 13,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 2,0</t>
+          <t>-4,31; 2,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 2,11</t>
+          <t>-4,13; 2,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 3,07</t>
+          <t>-5,44; 3,47</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-35,43%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-8,32%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-1,38%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-22,38%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-35,43%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-8,32%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-42,99%</t>
+          <t>-39,28%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-63,21; 183,74</t>
+          <t>-81,55; 114,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-67,56; 114,21</t>
+          <t>-69,28; 157,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 470,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-83,12; 101,75</t>
+          <t>-66,62; 170,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-64,66; 137,42</t>
+          <t>-70,23; 108,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 464,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-61,96; 62,64</t>
+          <t>-62,24; 81,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,43; 79,17</t>
+          <t>-56,49; 77,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-90,16; 100,76</t>
+          <t>-90,12; 132,45</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,51</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-3,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,96</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,23</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>-0,07</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 0,7</t>
+          <t>-3,22; 4,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 7,24</t>
+          <t>-3,45; 3,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 15,56</t>
+          <t>-4,57; 8,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 4,18</t>
+          <t>-7,35; 0,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 3,61</t>
+          <t>-2,5; 7,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 7,69</t>
+          <t>-5,85; 15,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 1,35</t>
+          <t>-4,19; 1,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 4,2</t>
+          <t>-2,11; 4,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 6,84</t>
+          <t>-4,13; 5,9</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-2,4%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-12,34%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-51,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>33,33%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>17,9%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-2,4%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-15,34%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-4,56%</t>
+          <t>-1,36%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-84,71; 37,59</t>
+          <t>-57,17; 184,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-39,5; 187,88</t>
+          <t>-62,24; 152,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 394,68</t>
+          <t>-100,0; 381,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,0; 184,75</t>
+          <t>-84,86; 25,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-63,1; 154,23</t>
+          <t>-35,7; 185,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 329,66</t>
+          <t>-100,0; 364,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-61,37; 43,87</t>
+          <t>-64,6; 41,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,18; 116,93</t>
+          <t>-34,37; 129,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-75,08; 183,42</t>
+          <t>-74,93; 158,53</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,64</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,39</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-4,63</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>1,26</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,86</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,41</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,64</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,39</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,3</t>
+          <t>-1,39</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,06</t>
+          <t>-3,21</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,57</t>
+          <t>-1,02; 4,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,57</t>
+          <t>-2,2; 3,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 4,45</t>
+          <t>-7,29; -1,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 4,36</t>
+          <t>-1,29; 4,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 2,88</t>
+          <t>-1,65; 3,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,16; -0,83</t>
+          <t>-5,57; 4,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,28</t>
+          <t>-0,33; 3,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,33</t>
+          <t>-1,25; 2,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,48; -0,09</t>
+          <t>-5,36; -0,15</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>19,67%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-55,32%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>14,73%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>10,05%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-16,52%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>19,67%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-51,45%</t>
+          <t>-16,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-36,23%</t>
+          <t>-38,0%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 49,02</t>
+          <t>-10,9; 60,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 50,21</t>
+          <t>-23,1; 44,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-58,45; 60,39</t>
+          <t>-77,6; -8,83</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 63,39</t>
+          <t>-13,43; 56,93</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-23,21; 41,72</t>
+          <t>-16,95; 47,06</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-78,11; -10,5</t>
+          <t>-60,89; 60,05</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 44,3</t>
+          <t>-3,49; 41,77</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 30,19</t>
+          <t>-13,75; 31,83</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-61,35; -1,46</t>
+          <t>-60,72; -2,07</t>
         </is>
       </c>
     </row>
